--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5503.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5503.xlsx
@@ -1403,6 +1403,9 @@
           <t>5503-04-02-FG</t>
         </is>
       </c>
+      <c r="F18" t="n">
+        <v>0.33</v>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>5503-04-02-FG</t>
@@ -1415,12 +1418,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | TAPDRILL@BORE = Air-Way per-size tap drill -02 0.33 (A1)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1440,6 +1443,9 @@
           <t>5503-06-04-FG</t>
         </is>
       </c>
+      <c r="F19" t="n">
+        <v>0.43</v>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>5503-06-04-FG</t>
@@ -1452,12 +1458,12 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | TAPDRILL@BORE = Air-Way per-size tap drill -04 0.43 (A1)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1477,6 +1483,9 @@
           <t>5503-08-06-FG</t>
         </is>
       </c>
+      <c r="F20" t="n">
+        <v>0.57</v>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>5503-08-06-FG</t>
@@ -1489,12 +1498,12 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | TAPDRILL@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1514,6 +1523,9 @@
           <t>5503-12-08-FG</t>
         </is>
       </c>
+      <c r="F21" t="n">
+        <v>0.7</v>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>5503-12-08-FG</t>
@@ -1526,12 +1538,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | TAPDRILL@BORE = Air-Way per-size tap drill -08 0.7 (A1)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1551,6 +1563,9 @@
           <t>5503-16-12-FG</t>
         </is>
       </c>
+      <c r="F22" t="n">
+        <v>0.91</v>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>5503-16-12-FG</t>
@@ -1563,12 +1578,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | TAPDRILL@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1736,6 +1751,9 @@
       <c r="E25" t="n">
         <v>1.5</v>
       </c>
+      <c r="F25" t="n">
+        <v>1.72</v>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>5503-24-24-FG</t>
@@ -1748,12 +1766,12 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D@BORE, N3@DRIVE, N4@DRIVE, PORTDEPTH@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5503-24-24 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: D@BORE, N3@DRIVE, N4@DRIVE, PORTDEPTH@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5503-24-24 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5503-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5503-24-24-FG (PARTcommunity / CADENAS, D@BORE=AD, N3@DRIVE=N1, N4@DRIVE=N, PORTDEPTH@BORE=BA; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5503-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5503-24-24-FG (PARTcommunity / CADENAS, D@BORE=AD, N3@DRIVE=N1, N4@DRIVE=N, PORTDEPTH@BORE=BA; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1790,6 +1808,9 @@
       <c r="E26" t="n">
         <v>1.938</v>
       </c>
+      <c r="F26" t="n">
+        <v>2.2</v>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>5503-32-32-FG</t>
@@ -1802,12 +1823,12 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>[BRENNAN-CAD 2026-10-21: D@BORE, N3@DRIVE, N4@DRIVE, PORTDEPTH@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5503-32-32 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: D@BORE, N3@DRIVE, N4@DRIVE, PORTDEPTH@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5503-32-32 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5503-32-32 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5503-32-32-FG (PARTcommunity / CADENAS, D@BORE=AD, N3@DRIVE=N1, N4@DRIVE=N, PORTDEPTH@BORE=BA; user 2026-10-21 "yes you can use them following my rule")</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5503-32-32 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5503-32-32-FG (PARTcommunity / CADENAS, D@BORE=AD, N3@DRIVE=N1, N4@DRIVE=N, PORTDEPTH@BORE=BA; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">

--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5503.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5503.xlsx
@@ -1748,12 +1748,21 @@
       <c r="C25" t="n">
         <v>1.69</v>
       </c>
+      <c r="D25" t="n">
+        <v>2.562</v>
+      </c>
       <c r="E25" t="n">
         <v>1.5</v>
       </c>
       <c r="F25" t="n">
         <v>1.72</v>
       </c>
+      <c r="G25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.9</v>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>5503-24-24-FG</t>
@@ -1761,17 +1770,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: D@BORE, N3@DRIVE, N4@DRIVE, PORTDEPTH@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5503-24-24 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: D@BORE, N3@DRIVE, N4@DRIVE, PORTDEPTH@BORE, W@HEX, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5503-24-24 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5503-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5503-24-24-FG (PARTcommunity / CADENAS, D@BORE=AD, N3@DRIVE=N1, N4@DRIVE=N, PORTDEPTH@BORE=BA; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5503-24-24 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5503-24-24-FG (PARTcommunity / CADENAS, D@BORE=AD, N3@DRIVE=N1, N4@DRIVE=N, PORTDEPTH@BORE=BA, W@HEX=Y, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -24 1.72 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1805,12 +1814,21 @@
       <c r="C26" t="n">
         <v>2.19</v>
       </c>
+      <c r="D26" t="n">
+        <v>2.812</v>
+      </c>
       <c r="E26" t="n">
         <v>1.938</v>
       </c>
       <c r="F26" t="n">
         <v>2.2</v>
       </c>
+      <c r="G26" t="n">
+        <v>2.375</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.375</v>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>5503-32-32-FG</t>
@@ -1818,17 +1836,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: D@BORE, N3@DRIVE, N4@DRIVE, PORTDEPTH@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5503-32-32 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: D@BORE, N3@DRIVE, N4@DRIVE, PORTDEPTH@BORE, W@HEX, THDMAJ_A1@DRIVE, THDMAJ_A2@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5503-32-32 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5503-32-32 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5503-32-32-FG (PARTcommunity / CADENAS, D@BORE=AD, N3@DRIVE=N1, N4@DRIVE=N, PORTDEPTH@BORE=BA; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5503-32-32 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 5503-32-32-FG (PARTcommunity / CADENAS, D@BORE=AD, N3@DRIVE=N1, N4@DRIVE=N, PORTDEPTH@BORE=BA, W@HEX=Y, THDMAJ_A1@DRIVE=A1THD, THDMAJ_A2@DRIVE=A2THD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
